--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762161</v>
       </c>
       <c r="B2" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762162</v>
       </c>
       <c r="B8" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762168</v>
       </c>
       <c r="B9" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762142</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762155</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762160</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762165</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762169</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762192</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762141</v>
       </c>
       <c r="B16" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762159</v>
       </c>
       <c r="B17" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762144</v>
       </c>
       <c r="B18" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762147</v>
       </c>
       <c r="B19" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762145</v>
       </c>
       <c r="B20" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762146</v>
       </c>
       <c r="B21" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136762148</v>
       </c>
       <c r="B22" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136762150</v>
       </c>
       <c r="B23" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136762151</v>
       </c>
       <c r="B24" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136762152</v>
       </c>
       <c r="B25" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136762189</v>
       </c>
       <c r="B26" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136762193</v>
       </c>
       <c r="B27" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136762154</v>
       </c>
       <c r="B28" t="n">
-        <v>79732</v>
+        <v>79736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136762149</v>
       </c>
       <c r="B29" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136762191</v>
       </c>
       <c r="B30" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136762190</v>
       </c>
       <c r="B31" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762161</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762162</v>
       </c>
       <c r="B8" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762168</v>
       </c>
       <c r="B9" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762142</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762155</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762160</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762165</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762169</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762192</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762141</v>
       </c>
       <c r="B16" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762159</v>
       </c>
       <c r="B17" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762144</v>
       </c>
       <c r="B18" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762147</v>
       </c>
       <c r="B19" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762145</v>
       </c>
       <c r="B20" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762146</v>
       </c>
       <c r="B21" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136762148</v>
       </c>
       <c r="B22" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136762150</v>
       </c>
       <c r="B23" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136762151</v>
       </c>
       <c r="B24" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136762152</v>
       </c>
       <c r="B25" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136762189</v>
       </c>
       <c r="B26" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136762193</v>
       </c>
       <c r="B27" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136762154</v>
       </c>
       <c r="B28" t="n">
-        <v>79736</v>
+        <v>79738</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136762149</v>
       </c>
       <c r="B29" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136762191</v>
       </c>
       <c r="B30" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136762190</v>
       </c>
       <c r="B31" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762161</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762162</v>
       </c>
       <c r="B8" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762168</v>
       </c>
       <c r="B9" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762142</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762155</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762160</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762165</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762169</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762192</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762141</v>
       </c>
       <c r="B16" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762159</v>
       </c>
       <c r="B17" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762144</v>
       </c>
       <c r="B18" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762147</v>
       </c>
       <c r="B19" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762145</v>
       </c>
       <c r="B20" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762146</v>
       </c>
       <c r="B21" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136762148</v>
       </c>
       <c r="B22" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136762150</v>
       </c>
       <c r="B23" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136762151</v>
       </c>
       <c r="B24" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136762152</v>
       </c>
       <c r="B25" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136762189</v>
       </c>
       <c r="B26" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136762193</v>
       </c>
       <c r="B27" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136762154</v>
       </c>
       <c r="B28" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136762149</v>
       </c>
       <c r="B29" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136762191</v>
       </c>
       <c r="B30" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136762190</v>
       </c>
       <c r="B31" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762161</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762162</v>
       </c>
       <c r="B8" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762168</v>
       </c>
       <c r="B9" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762142</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762155</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762160</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762165</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762169</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762192</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762141</v>
       </c>
       <c r="B16" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762159</v>
       </c>
       <c r="B17" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762144</v>
       </c>
       <c r="B18" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762147</v>
       </c>
       <c r="B19" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762145</v>
       </c>
       <c r="B20" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762146</v>
       </c>
       <c r="B21" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136762148</v>
       </c>
       <c r="B22" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136762150</v>
       </c>
       <c r="B23" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136762151</v>
       </c>
       <c r="B24" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136762152</v>
       </c>
       <c r="B25" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136762189</v>
       </c>
       <c r="B26" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136762193</v>
       </c>
       <c r="B27" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136762154</v>
       </c>
       <c r="B28" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136762149</v>
       </c>
       <c r="B29" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136762191</v>
       </c>
       <c r="B30" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136762190</v>
       </c>
       <c r="B31" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -4900,7 +4900,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762161</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762162</v>
       </c>
       <c r="B8" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762168</v>
       </c>
       <c r="B9" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762142</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762155</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762160</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762165</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762169</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762192</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762141</v>
       </c>
       <c r="B16" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762159</v>
       </c>
       <c r="B17" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762144</v>
       </c>
       <c r="B18" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762147</v>
       </c>
       <c r="B19" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762145</v>
       </c>
       <c r="B20" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762146</v>
       </c>
       <c r="B21" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136762148</v>
       </c>
       <c r="B22" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136762150</v>
       </c>
       <c r="B23" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136762151</v>
       </c>
       <c r="B24" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136762152</v>
       </c>
       <c r="B25" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136762189</v>
       </c>
       <c r="B26" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136762193</v>
       </c>
       <c r="B27" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136762154</v>
       </c>
       <c r="B28" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136762149</v>
       </c>
       <c r="B29" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136762191</v>
       </c>
       <c r="B30" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136762190</v>
       </c>
       <c r="B31" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762161</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762162</v>
       </c>
       <c r="B8" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762168</v>
       </c>
       <c r="B9" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762142</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762155</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762160</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762165</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762169</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762192</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762141</v>
       </c>
       <c r="B16" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762159</v>
       </c>
       <c r="B17" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762144</v>
       </c>
       <c r="B18" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762147</v>
       </c>
       <c r="B19" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762145</v>
       </c>
       <c r="B20" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762146</v>
       </c>
       <c r="B21" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136762148</v>
       </c>
       <c r="B22" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136762150</v>
       </c>
       <c r="B23" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136762151</v>
       </c>
       <c r="B24" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136762152</v>
       </c>
       <c r="B25" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136762189</v>
       </c>
       <c r="B26" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136762193</v>
       </c>
       <c r="B27" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136762154</v>
       </c>
       <c r="B28" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136762149</v>
       </c>
       <c r="B29" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136762191</v>
       </c>
       <c r="B30" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136762190</v>
       </c>
       <c r="B31" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136762156</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>136762157</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136762158</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>136762195</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>136762197</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136762143</v>
       </c>
       <c r="B37" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>136762163</v>
       </c>
       <c r="B38" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762161</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762162</v>
       </c>
       <c r="B8" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762168</v>
       </c>
       <c r="B9" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762142</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762155</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762160</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762165</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762169</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762192</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762141</v>
       </c>
       <c r="B16" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762159</v>
       </c>
       <c r="B17" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762144</v>
       </c>
       <c r="B18" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762147</v>
       </c>
       <c r="B19" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762145</v>
       </c>
       <c r="B20" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762146</v>
       </c>
       <c r="B21" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>136762148</v>
       </c>
       <c r="B22" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>136762150</v>
       </c>
       <c r="B23" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136762151</v>
       </c>
       <c r="B24" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136762152</v>
       </c>
       <c r="B25" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>136762189</v>
       </c>
       <c r="B26" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>136762193</v>
       </c>
       <c r="B27" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>136762154</v>
       </c>
       <c r="B28" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136762149</v>
       </c>
       <c r="B29" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>136762191</v>
       </c>
       <c r="B30" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>136762190</v>
       </c>
       <c r="B31" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>136762156</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>136762157</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136762158</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>136762195</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>136762197</v>
       </c>
       <c r="B36" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136762143</v>
       </c>
       <c r="B37" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>136762163</v>
       </c>
       <c r="B38" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -2837,11 +2837,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Vimyrorna, Mpd</t>
@@ -4074,11 +4070,7 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Vimyrorna, Mpd</t>
@@ -4196,11 +4188,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Vimyrorna, Mpd</t>
@@ -4318,11 +4306,7 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Vimyrorna, Mpd</t>
@@ -4440,11 +4424,7 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vimyrorna, Mpd</t>
@@ -4562,11 +4542,7 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vimyrorna, Mpd</t>
@@ -4688,11 +4664,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Vimyrorna, Mpd</t>
@@ -4809,11 +4781,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Vimyrorna, Mpd</t>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762141</v>
       </c>
       <c r="B16" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762159</v>
       </c>
       <c r="B17" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762161</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762162</v>
       </c>
       <c r="B8" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762168</v>
       </c>
       <c r="B9" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762142</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762155</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762160</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762165</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762169</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762192</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762141</v>
       </c>
       <c r="B16" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762159</v>
       </c>
       <c r="B17" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762144</v>
       </c>
       <c r="B18" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762147</v>
       </c>
       <c r="B19" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762145</v>
       </c>
       <c r="B20" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762146</v>
       </c>
       <c r="B21" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136762148</v>
       </c>
       <c r="B22" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136762150</v>
       </c>
       <c r="B23" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>136762151</v>
       </c>
       <c r="B24" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>136762152</v>
       </c>
       <c r="B25" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>136762189</v>
       </c>
       <c r="B26" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>136762193</v>
       </c>
       <c r="B27" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136762154</v>
       </c>
       <c r="B28" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>136762149</v>
       </c>
       <c r="B29" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>136762191</v>
       </c>
       <c r="B30" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>136762190</v>
       </c>
       <c r="B31" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>136762156</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>136762157</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136762158</v>
       </c>
       <c r="B34" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>136762195</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136762197</v>
       </c>
       <c r="B36" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>136762143</v>
       </c>
       <c r="B37" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>136762163</v>
       </c>
       <c r="B38" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136762161</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136762162</v>
       </c>
       <c r="B8" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136762168</v>
       </c>
       <c r="B9" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136762142</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136762155</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136762160</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136762165</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136762169</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136762192</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136762141</v>
       </c>
       <c r="B16" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136762159</v>
       </c>
       <c r="B17" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136762144</v>
       </c>
       <c r="B18" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>136762147</v>
       </c>
       <c r="B19" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>136762145</v>
       </c>
       <c r="B20" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136762146</v>
       </c>
       <c r="B21" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>136762148</v>
       </c>
       <c r="B22" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>136762150</v>
       </c>
       <c r="B23" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>136762151</v>
       </c>
       <c r="B24" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>136762152</v>
       </c>
       <c r="B25" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>136762189</v>
       </c>
       <c r="B26" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>136762193</v>
       </c>
       <c r="B27" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136762154</v>
       </c>
       <c r="B28" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>136762149</v>
       </c>
       <c r="B29" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>136762191</v>
       </c>
       <c r="B30" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>136762190</v>
       </c>
       <c r="B31" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>136762156</v>
       </c>
       <c r="B32" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>136762157</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>136762158</v>
       </c>
       <c r="B34" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>136762195</v>
       </c>
       <c r="B35" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>136762197</v>
       </c>
       <c r="B36" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>136762143</v>
       </c>
       <c r="B37" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>136762163</v>
       </c>
       <c r="B38" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26013-2024 artfynd.xlsx
+++ b/artfynd/A 26013-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136762166</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136762188</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136762153</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136762167</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136762194</v>
       </c>
       <c r="B7" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136762164</v>
       </c>
       <c r="B39" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136762196</v>
       </c>
       <c r="B40" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
